--- a/data/trans_camb/POLIPATOLOGIA_2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 11,86</t>
+          <t>-2,11; 11,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 13,66</t>
+          <t>-0,16; 13,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 17,22</t>
+          <t>3,04; 17,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 24,35</t>
+          <t>6,84; 23,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 24,41</t>
+          <t>7,1; 23,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 14,04</t>
+          <t>1,72; 14,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 15,71</t>
+          <t>4,57; 15,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,29</t>
+          <t>5,82; 15,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 14,34</t>
+          <t>3,77; 13,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 78,67</t>
+          <t>-9,68; 75,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 94,85</t>
+          <t>-1,82; 86,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 110,18</t>
+          <t>13,93; 114,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,25; 110,65</t>
+          <t>22,39; 109,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,96; 113,6</t>
+          <t>24,07; 107,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 65,21</t>
+          <t>5,05; 70,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 84,69</t>
+          <t>18,8; 82,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,66; 86,89</t>
+          <t>23,27; 82,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,08; 75,84</t>
+          <t>14,54; 70,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 7,86</t>
+          <t>-2,14; 8,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 8,44</t>
+          <t>-1,25; 9,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,49</t>
+          <t>1,92; 13,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 0,33</t>
+          <t>-11,95; 0,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 1,9</t>
+          <t>-11,28; 0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 5,48</t>
+          <t>-6,4; 4,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,73</t>
+          <t>-5,89; 2,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 3,45</t>
+          <t>-4,65; 3,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 7,33</t>
+          <t>-0,76; 7,54</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 49,93</t>
+          <t>-10,33; 54,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 53,05</t>
+          <t>-5,78; 56,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 84,57</t>
+          <t>9,37; 85,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 1,33</t>
+          <t>-27,31; 0,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 4,68</t>
+          <t>-26,3; 1,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 14,61</t>
+          <t>-14,68; 12,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 10,0</t>
+          <t>-18,56; 9,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 12,87</t>
+          <t>-15,05; 12,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 26,89</t>
+          <t>-2,15; 27,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 17,7</t>
+          <t>4,75; 18,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 8,43</t>
+          <t>-3,55; 8,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 25,85</t>
+          <t>12,77; 25,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 13,07</t>
+          <t>-1,57; 13,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 8,74</t>
+          <t>-5,63; 8,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 22,86</t>
+          <t>9,47; 22,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 13,1</t>
+          <t>3,91; 13,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,02</t>
+          <t>-2,71; 6,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,94; 22,32</t>
+          <t>12,75; 22,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,02; 127,82</t>
+          <t>23,12; 135,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 63,01</t>
+          <t>-17,36; 62,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,36; 191,09</t>
+          <t>64,28; 185,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 47,54</t>
+          <t>-5,02; 48,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 32,14</t>
+          <t>-16,1; 33,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,15; 88,38</t>
+          <t>28,01; 84,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,93; 60,96</t>
+          <t>13,62; 62,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 32,83</t>
+          <t>-10,48; 31,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,05; 104,3</t>
+          <t>47,09; 103,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 9,48</t>
+          <t>-2,7; 9,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,04</t>
+          <t>1,62; 14,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 22,83</t>
+          <t>8,16; 22,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 20,23</t>
+          <t>6,45; 20,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 19,3</t>
+          <t>5,05; 19,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,79; 42,19</t>
+          <t>9,96; 41,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,11</t>
+          <t>3,28; 12,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,81</t>
+          <t>5,39; 15,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 36,8</t>
+          <t>12,3; 34,66</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 53,4</t>
+          <t>-12,53; 50,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,29; 82,46</t>
+          <t>6,73; 79,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,46; 126,56</t>
+          <t>32,8; 123,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,32; 74,54</t>
+          <t>19,24; 77,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,16; 70,96</t>
+          <t>13,59; 69,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,71; 157,27</t>
+          <t>31,2; 143,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,11; 54,8</t>
+          <t>11,36; 54,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,39; 61,48</t>
+          <t>18,36; 63,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46,25; 149,65</t>
+          <t>45,23; 138,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,74; 23,52</t>
+          <t>6,69; 23,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 17,5</t>
+          <t>2,62; 17,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,77; 27,81</t>
+          <t>12,3; 27,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,21; 38,45</t>
+          <t>19,36; 38,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 19,01</t>
+          <t>1,28; 19,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 25,27</t>
+          <t>-8,08; 26,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,56; 28,72</t>
+          <t>15,89; 29,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,45; 15,88</t>
+          <t>4,24; 15,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,3; 25,07</t>
+          <t>4,42; 25,29</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>46,23; 250,05</t>
+          <t>39,41; 249,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15,19; 180,81</t>
+          <t>14,91; 189,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74,45; 300,92</t>
+          <t>71,66; 294,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54,74; 153,29</t>
+          <t>55,62; 154,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,61; 74,35</t>
+          <t>2,49; 77,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 89,74</t>
+          <t>-21,08; 90,56</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,49; 152,02</t>
+          <t>63,16; 152,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,31; 83,5</t>
+          <t>16,7; 83,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,96; 126,3</t>
+          <t>20,85; 133,97</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,58; 21,47</t>
+          <t>7,12; 21,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 11,91</t>
+          <t>-1,34; 12,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,72; 31,54</t>
+          <t>17,59; 31,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,78; 17,68</t>
+          <t>2,23; 18,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 6,76</t>
+          <t>-8,15; 7,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,21; 21,36</t>
+          <t>6,11; 21,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,07; 17,69</t>
+          <t>6,54; 17,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,88</t>
+          <t>-3,33; 7,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,77; 24,2</t>
+          <t>13,45; 24,54</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36,11; 147,14</t>
+          <t>33,03; 147,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 76,05</t>
+          <t>-7,33; 83,21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>80,65; 212,15</t>
+          <t>79,79; 228,89</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4,29; 55,5</t>
+          <t>5,74; 58,66</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 22,35</t>
+          <t>-20,74; 25,71</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,98; 68,88</t>
+          <t>15,97; 69,6</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>22,92; 72,53</t>
+          <t>21,64; 73,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 32,09</t>
+          <t>-10,85; 29,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>46,65; 99,95</t>
+          <t>43,84; 98,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,6; 12,45</t>
+          <t>2,85; 11,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,86</t>
+          <t>-2,25; 6,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15,1; 26,88</t>
+          <t>14,62; 25,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,87; 14,91</t>
+          <t>4,36; 14,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 7,72</t>
+          <t>-1,91; 8,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,71; 57,53</t>
+          <t>30,41; 56,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,85; 12,0</t>
+          <t>4,98; 12,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,93</t>
+          <t>-0,69; 6,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>25,0; 51,04</t>
+          <t>24,66; 48,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,5; 74,38</t>
+          <t>13,3; 68,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 39,24</t>
+          <t>-10,83; 39,03</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69,06; 156,46</t>
+          <t>68,42; 148,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15,41; 54,8</t>
+          <t>13,94; 53,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 29,03</t>
+          <t>-5,88; 29,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>98,96; 212,05</t>
+          <t>98,39; 215,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,05; 51,37</t>
+          <t>18,82; 51,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 26,03</t>
+          <t>-2,71; 27,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>96,6; 214,31</t>
+          <t>96,98; 213,45</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,06; -1,21</t>
+          <t>-10,05; -1,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 6,24</t>
+          <t>-2,85; 5,79</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 3,79</t>
+          <t>-17,08; 3,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,14; -2,81</t>
+          <t>-12,21; -2,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 3,6</t>
+          <t>-6,51; 3,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,35</t>
+          <t>-4,13; 5,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -3,09</t>
+          <t>-9,88; -3,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,43</t>
+          <t>-3,93; 3,13</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 2,31</t>
+          <t>-14,99; 2,51</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -5,36</t>
+          <t>-36,56; -5,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 27,22</t>
+          <t>-10,61; 25,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 15,48</t>
+          <t>-63,9; 15,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,73; -8,29</t>
+          <t>-30,53; -7,17</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 10,42</t>
+          <t>-16,27; 10,41</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 15,6</t>
+          <t>-10,4; 15,38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-28,76; -10,44</t>
+          <t>-29,76; -11,25</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 11,71</t>
+          <t>-11,82; 10,5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 7,45</t>
+          <t>-46,39; 8,38</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,68</t>
+          <t>2,64; 6,46</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,16</t>
+          <t>2,02; 6,1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4,45; 13,78</t>
+          <t>3,88; 13,74</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,54</t>
+          <t>2,91; 7,78</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,86</t>
+          <t>0,25; 5,14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,1</t>
+          <t>11,53; 24,7</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,41</t>
+          <t>3,3; 6,48</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,84</t>
+          <t>1,79; 4,91</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,57; 19,1</t>
+          <t>9,49; 18,67</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>11,93; 35,01</t>
+          <t>12,67; 34,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10,27; 32,93</t>
+          <t>9,85; 32,38</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>23,42; 71,63</t>
+          <t>20,0; 71,67</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,1; 23,37</t>
+          <t>8,22; 23,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,5; 15,04</t>
+          <t>0,73; 16,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>32,79; 74,1</t>
+          <t>34,13; 75,17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,51; 24,46</t>
+          <t>11,99; 24,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,54; 18,65</t>
+          <t>6,39; 18,83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>35,07; 71,72</t>
+          <t>35,35; 70,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>9,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>8,1</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 11,25</t>
+          <t>-1,97; 11,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,34</t>
+          <t>-0,24; 12,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 17,03</t>
+          <t>2,72; 15,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 23,4</t>
+          <t>6,35; 23,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,1; 23,54</t>
+          <t>7,24; 23,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,97</t>
+          <t>-0,23; 13,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 15,65</t>
+          <t>4,17; 15,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,92</t>
+          <t>5,69; 16,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 13,97</t>
+          <t>3,12; 12,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>36,82%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 75,0</t>
+          <t>-10,2; 74,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 86,5</t>
+          <t>-1,36; 82,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,93; 114,01</t>
+          <t>10,7; 99,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 109,88</t>
+          <t>21,14; 104,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,07; 107,65</t>
+          <t>24,95; 109,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 70,9</t>
+          <t>-0,27; 64,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 82,96</t>
+          <t>16,9; 80,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,27; 82,74</t>
+          <t>22,76; 84,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 70,67</t>
+          <t>12,24; 65,76</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 8,5</t>
+          <t>-2,7; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 9,04</t>
+          <t>-1,58; 8,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,46</t>
+          <t>2,25; 13,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,06</t>
+          <t>-11,97; 0,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,75</t>
+          <t>-11,37; 1,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,69</t>
+          <t>-6,47; 4,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,68</t>
+          <t>-5,32; 3,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,47</t>
+          <t>-4,5; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 7,54</t>
+          <t>-0,82; 7,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,37%</t>
+          <t>-1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 54,29</t>
+          <t>-13,63; 53,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 56,89</t>
+          <t>-8,27; 53,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 85,56</t>
+          <t>10,39; 84,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 0,19</t>
+          <t>-27,44; 0,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 1,97</t>
+          <t>-26,12; 3,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 12,38</t>
+          <t>-14,52; 13,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 9,77</t>
+          <t>-16,76; 11,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 12,71</t>
+          <t>-14,37; 13,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 27,44</t>
+          <t>-2,61; 28,06</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,02</t>
+          <t>19,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>16,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,66</t>
+          <t>18,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 18,25</t>
+          <t>4,69; 17,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,27</t>
+          <t>-3,57; 8,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 25,09</t>
+          <t>13,03; 26,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 13,44</t>
+          <t>-2,03; 13,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 8,77</t>
+          <t>-6,35; 7,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 22,64</t>
+          <t>10,46; 23,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 13,75</t>
+          <t>3,33; 13,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,7</t>
+          <t>-2,58; 7,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,75; 22,44</t>
+          <t>13,14; 22,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115,3%</t>
+          <t>117,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 135,51</t>
+          <t>22,48; 128,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 62,79</t>
+          <t>-18,2; 68,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,28; 185,62</t>
+          <t>67,52; 205,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 48,83</t>
+          <t>-5,63; 48,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 33,27</t>
+          <t>-18,58; 28,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,01; 84,86</t>
+          <t>29,53; 85,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,62; 62,78</t>
+          <t>12,68; 64,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 31,04</t>
+          <t>-10,42; 33,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,09; 103,5</t>
+          <t>48,72; 109,37</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,9</t>
+          <t>12,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,0</t>
+          <t>16,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20,12</t>
+          <t>14,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 9,35</t>
+          <t>-3,12; 9,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,24</t>
+          <t>1,21; 14,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 22,58</t>
+          <t>5,12; 20,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 20,5</t>
+          <t>7,14; 20,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,19</t>
+          <t>5,61; 19,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 41,12</t>
+          <t>9,79; 23,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,83</t>
+          <t>3,61; 13,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,22</t>
+          <t>5,1; 14,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 34,66</t>
+          <t>10,07; 19,99</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 50,49</t>
+          <t>-12,52; 53,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,73; 79,9</t>
+          <t>4,78; 82,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,8; 123,92</t>
+          <t>22,75; 116,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,24; 77,17</t>
+          <t>21,38; 74,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,59; 69,07</t>
+          <t>16,76; 70,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,2; 143,02</t>
+          <t>28,24; 87,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,36; 54,58</t>
+          <t>12,27; 56,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,36; 63,1</t>
+          <t>18,27; 62,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45,23; 138,16</t>
+          <t>36,22; 84,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20,54</t>
+          <t>18,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,16</t>
+          <t>21,48</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>20,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,69; 23,56</t>
+          <t>7,56; 24,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 17,82</t>
+          <t>2,54; 17,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,3; 27,37</t>
+          <t>10,35; 25,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,36; 38,49</t>
+          <t>19,26; 37,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 19,35</t>
+          <t>1,0; 19,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 26,23</t>
+          <t>12,71; 29,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,89; 29,31</t>
+          <t>15,24; 28,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 15,93</t>
+          <t>4,1; 16,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 25,29</t>
+          <t>15,02; 26,41</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161,04%</t>
+          <t>144,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>39,41; 249,18</t>
+          <t>46,38; 241,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14,91; 189,43</t>
+          <t>17,56; 195,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71,66; 294,22</t>
+          <t>59,87; 272,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55,62; 154,23</t>
+          <t>55,72; 154,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,49; 77,46</t>
+          <t>3,29; 77,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 90,56</t>
+          <t>33,52; 115,28</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,16; 152,06</t>
+          <t>59,88; 153,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16,7; 83,57</t>
+          <t>16,39; 88,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20,85; 133,97</t>
+          <t>60,0; 147,61</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24,77</t>
+          <t>24,2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,77</t>
+          <t>13,61</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19,08</t>
+          <t>18,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>7,12; 21,62</t>
+          <t>6,92; 21,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 12,61</t>
+          <t>-1,42; 12,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17,59; 31,89</t>
+          <t>17,31; 31,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,23; 18,55</t>
+          <t>1,84; 17,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 7,67</t>
+          <t>-8,96; 7,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,11; 21,54</t>
+          <t>6,43; 20,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,54; 17,54</t>
+          <t>6,88; 17,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,35</t>
+          <t>-2,75; 7,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13,45; 24,54</t>
+          <t>13,73; 23,5</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>134,81%</t>
+          <t>131,72%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33,03; 147,34</t>
+          <t>29,37; 143,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 83,21</t>
+          <t>-6,98; 85,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79,79; 228,89</t>
+          <t>74,66; 210,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,74; 58,66</t>
+          <t>4,72; 55,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 25,71</t>
+          <t>-23,06; 22,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,97; 69,6</t>
+          <t>15,87; 66,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,64; 73,65</t>
+          <t>23,45; 72,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 29,92</t>
+          <t>-9,36; 32,4</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43,84; 98,95</t>
+          <t>45,33; 96,78</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20,26</t>
+          <t>20,9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,19</t>
+          <t>32,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33,03</t>
+          <t>26,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,93</t>
+          <t>2,4; 12,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,75</t>
+          <t>-2,01; 6,94</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14,62; 25,46</t>
+          <t>15,7; 26,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,36; 14,59</t>
+          <t>4,34; 15,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 8,08</t>
+          <t>-2,22; 7,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,41; 56,12</t>
+          <t>27,44; 37,54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,98; 12,09</t>
+          <t>4,83; 12,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,29</t>
+          <t>-1,19; 6,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24,66; 48,11</t>
+          <t>23,54; 30,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104,79%</t>
+          <t>108,05%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>138,28%</t>
+          <t>108,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>133,93%</t>
+          <t>108,92%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>13,3; 68,77</t>
+          <t>11,65; 73,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 39,03</t>
+          <t>-9,77; 39,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>68,42; 148,26</t>
+          <t>73,53; 155,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,94; 53,7</t>
+          <t>13,22; 56,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 29,49</t>
+          <t>-7,06; 27,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>98,39; 215,34</t>
+          <t>83,1; 141,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,82; 51,92</t>
+          <t>19,38; 54,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 27,65</t>
+          <t>-4,56; 26,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>96,98; 213,45</t>
+          <t>88,49; 136,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,04</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,05; -1,24</t>
+          <t>-10,26; -1,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,79</t>
+          <t>-2,88; 6,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 3,79</t>
+          <t>-3,21; 5,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-12,21; -2,51</t>
+          <t>-12,07; -2,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,67</t>
+          <t>-6,72; 3,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,25</t>
+          <t>-4,98; 4,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -3,34</t>
+          <t>-9,31; -3,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,13</t>
+          <t>-3,37; 3,03</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 2,51</t>
+          <t>-2,69; 3,7</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-20,07%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>-0,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-11,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-36,56; -5,5</t>
+          <t>-37,24; -6,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 25,42</t>
+          <t>-11,1; 26,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 15,21</t>
+          <t>-11,82; 25,9</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,53; -7,17</t>
+          <t>-30,48; -7,65</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 10,41</t>
+          <t>-16,88; 9,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 15,38</t>
+          <t>-12,39; 12,11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,76; -11,25</t>
+          <t>-28,25; -10,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 10,5</t>
+          <t>-10,31; 10,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 8,38</t>
+          <t>-8,09; 12,27</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>12,52</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,84</t>
+          <t>12,63</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,5</t>
+          <t>12,66</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,46</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,1</t>
+          <t>2,04; 6,13</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,88; 13,74</t>
+          <t>10,31; 14,98</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,78</t>
+          <t>2,85; 7,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,14</t>
+          <t>0,1; 4,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,7</t>
+          <t>10,43; 14,76</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,48</t>
+          <t>3,24; 6,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,91</t>
+          <t>1,91; 4,94</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>9,49; 18,67</t>
+          <t>10,98; 14,26</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>12,67; 34,49</t>
+          <t>10,63; 34,53</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>9,85; 32,38</t>
+          <t>9,23; 32,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>20,0; 71,67</t>
+          <t>49,57; 79,72</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,22; 23,97</t>
+          <t>8,34; 23,05</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,73; 16,32</t>
+          <t>0,22; 15,09</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,13; 75,17</t>
+          <t>29,65; 45,36</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,99; 24,96</t>
+          <t>11,78; 24,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,39; 18,83</t>
+          <t>6,93; 19,13</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>35,35; 70,05</t>
+          <t>40,05; 55,09</t>
         </is>
       </c>
     </row>
